--- a/Bao cao/VIB/VIB_Model_2026-06.xlsx
+++ b/Bao cao/VIB/VIB_Model_2026-06.xlsx
@@ -24,6 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Investment_Thesis" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Summary_Snapshot" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_PE_PB_History" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Credit_Funding_Growth" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -141,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +182,8 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2766,6 +2769,662 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Quý</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Tổng Tín dụng (tỷ VND)</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Tổng Huy động (tỷ VND)</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Tăng trưởng Tín dụng YTD (%)</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Tăng trưởng Huy động YTD (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Q2/18</t>
+        </is>
+      </c>
+      <c r="B2" s="29" t="n">
+        <v>86200.406</v>
+      </c>
+      <c r="C2" s="29" t="n">
+        <v>82885.63</v>
+      </c>
+      <c r="D2" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Q3/18</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="n">
+        <v>89687.95699999999</v>
+      </c>
+      <c r="C3" s="29" t="n">
+        <v>88978.30900000001</v>
+      </c>
+      <c r="D3" s="30" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="E3" s="30" t="n">
+        <v>0.0735</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Q4/18</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="n">
+        <v>95260.822</v>
+      </c>
+      <c r="C4" s="29" t="n">
+        <v>95015.06099999999</v>
+      </c>
+      <c r="D4" s="30" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>0.1463</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Q1/19</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="n">
+        <v>100869.689</v>
+      </c>
+      <c r="C5" s="29" t="n">
+        <v>99123.031</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>0.05889999999999999</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>0.0432</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Q2/19</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>113386.619</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>114415.413</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>0.1903</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>0.2042</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Q3/19</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>121966.052</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>128964.391</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>0.3573</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Q4/19</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="n">
+        <v>127942.036</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>139511.891</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>0.4683</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Q1/20</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="n">
+        <v>133467.428</v>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>140817.396</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Q2/20</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="n">
+        <v>136276.52</v>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>147774.751</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>0.06509999999999999</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>0.0592</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Q3/20</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="n">
+        <v>147458.347</v>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>165710.24</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>0.1878</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Q4/20</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>167797.844</v>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>178919.358</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>0.2825</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Q1/21</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="n">
+        <v>175606.988</v>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>185354.246</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0.04650000000000001</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Q2/21</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="n">
+        <v>180970.774</v>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>197336.297</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>0.1029</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Q3/21</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="n">
+        <v>185703.815</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>197727.889</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>0.1051</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Q4/21</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="n">
+        <v>199116.43</v>
+      </c>
+      <c r="C16" s="29" t="n">
+        <v>215863.072</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>0.2065</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Q1/22</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="n">
+        <v>211470.497</v>
+      </c>
+      <c r="C17" s="29" t="n">
+        <v>226563.945</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0.0496</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Q2/22</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="n">
+        <v>218784.626</v>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>237871.336</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0.09880000000000001</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Q3/22</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="n">
+        <v>223283.589</v>
+      </c>
+      <c r="C19" s="29" t="n">
+        <v>224222.252</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0.0387</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Q4/22</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="n">
+        <v>228879.249</v>
+      </c>
+      <c r="C20" s="29" t="n">
+        <v>231898.758</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0.07429999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>Q1/23</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="n">
+        <v>226004.365</v>
+      </c>
+      <c r="C21" s="29" t="n">
+        <v>233108.23905</v>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>-0.0126</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>0.0052</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Q2/23</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="n">
+        <v>231347.002</v>
+      </c>
+      <c r="C22" s="29" t="n">
+        <v>233578.906</v>
+      </c>
+      <c r="D22" s="30" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="E22" s="30" t="n">
+        <v>0.0072</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Q3/23</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="n">
+        <v>241890.738</v>
+      </c>
+      <c r="C23" s="29" t="n">
+        <v>240012.8836</v>
+      </c>
+      <c r="D23" s="30" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Q4/23</t>
+        </is>
+      </c>
+      <c r="B24" s="29" t="n">
+        <v>262074.228</v>
+      </c>
+      <c r="C24" s="29" t="n">
+        <v>263176.32975</v>
+      </c>
+      <c r="D24" s="30" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="E24" s="30" t="n">
+        <v>0.1349</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>Q1/24</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="n">
+        <v>262910.844</v>
+      </c>
+      <c r="C25" s="29" t="n">
+        <v>261187.7725</v>
+      </c>
+      <c r="D25" s="30" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>-0.0076</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Q2/24</t>
+        </is>
+      </c>
+      <c r="B26" s="29" t="n">
+        <v>273996.195</v>
+      </c>
+      <c r="C26" s="29" t="n">
+        <v>266305.1065</v>
+      </c>
+      <c r="D26" s="30" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="E26" s="30" t="n">
+        <v>0.0119</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>Q3/24</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="n">
+        <v>292146.173</v>
+      </c>
+      <c r="C27" s="29" t="n">
+        <v>280182.65</v>
+      </c>
+      <c r="D27" s="30" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>0.0646</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Q4/24</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="n">
+        <v>318316.079</v>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>302402.543</v>
+      </c>
+      <c r="D28" s="30" t="n">
+        <v>0.2146</v>
+      </c>
+      <c r="E28" s="30" t="n">
+        <v>0.149</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>Q1/25</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="n">
+        <v>329264.074</v>
+      </c>
+      <c r="C29" s="29" t="n">
+        <v>311756.2396</v>
+      </c>
+      <c r="D29" s="30" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="E29" s="30" t="n">
+        <v>0.0309</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>Q2/25</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="n">
+        <v>351360.111</v>
+      </c>
+      <c r="C30" s="29" t="n">
+        <v>337488.7078</v>
+      </c>
+      <c r="D30" s="30" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="E30" s="30" t="n">
+        <v>0.116</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>Q3/25</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="n">
+        <v>367863.425</v>
+      </c>
+      <c r="C31" s="29" t="n">
+        <v>339271.879</v>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>0.1557</v>
+      </c>
+      <c r="E31" s="30" t="n">
+        <v>0.1219</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>Q4/25</t>
+        </is>
+      </c>
+      <c r="B32" s="29" t="n">
+        <v>377113.195</v>
+      </c>
+      <c r="C32" s="29" t="n">
+        <v>335619.0126</v>
+      </c>
+      <c r="D32" s="30" t="n">
+        <v>0.1847</v>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>0.1098</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>Q1/26</t>
+        </is>
+      </c>
+      <c r="B33" s="29" t="n">
+        <v>381361.994</v>
+      </c>
+      <c r="C33" s="29" t="n">
+        <v>361024.6676</v>
+      </c>
+      <c r="D33" s="30" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="E33" s="30" t="n">
+        <v>0.0757</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Bao cao/VIB/VIB_Model_2026-06.xlsx
+++ b/Bao cao/VIB/VIB_Model_2026-06.xlsx
@@ -2047,19 +2047,19 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>21702.85</v>
+        <v>42.38</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>18345.796</v>
+        <v>42.38</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>15123.396</v>
+        <v>42.38</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>20244.697</v>
+        <v>42.38</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>43794.655</v>
+        <v>0</v>
       </c>
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="10" t="n"/>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="B2" s="29" t="n">
-        <v>86200.406</v>
+        <v>87706.69</v>
       </c>
       <c r="C2" s="29" t="n">
         <v>82885.63</v>
@@ -2838,13 +2838,13 @@
         </is>
       </c>
       <c r="B3" s="29" t="n">
-        <v>89687.95699999999</v>
+        <v>89730.337</v>
       </c>
       <c r="C3" s="29" t="n">
         <v>88978.30900000001</v>
       </c>
       <c r="D3" s="30" t="n">
-        <v>0.0405</v>
+        <v>0.0231</v>
       </c>
       <c r="E3" s="30" t="n">
         <v>0.0735</v>
@@ -2857,13 +2857,13 @@
         </is>
       </c>
       <c r="B4" s="29" t="n">
-        <v>95260.822</v>
+        <v>95303.202</v>
       </c>
       <c r="C4" s="29" t="n">
         <v>95015.06099999999</v>
       </c>
       <c r="D4" s="30" t="n">
-        <v>0.1051</v>
+        <v>0.0866</v>
       </c>
       <c r="E4" s="30" t="n">
         <v>0.1463</v>
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="B5" s="29" t="n">
-        <v>100869.689</v>
+        <v>100912.069</v>
       </c>
       <c r="C5" s="29" t="n">
         <v>99123.031</v>
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="B6" s="29" t="n">
-        <v>113386.619</v>
+        <v>113428.999</v>
       </c>
       <c r="C6" s="29" t="n">
         <v>114415.413</v>
       </c>
       <c r="D6" s="30" t="n">
-        <v>0.1903</v>
+        <v>0.1902</v>
       </c>
       <c r="E6" s="30" t="n">
         <v>0.2042</v>
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>121966.052</v>
+        <v>122008.432</v>
       </c>
       <c r="C7" s="29" t="n">
         <v>128964.391</v>
       </c>
       <c r="D7" s="30" t="n">
-        <v>0.2803</v>
+        <v>0.2802</v>
       </c>
       <c r="E7" s="30" t="n">
         <v>0.3573</v>
@@ -2933,13 +2933,13 @@
         </is>
       </c>
       <c r="B8" s="29" t="n">
-        <v>127942.036</v>
+        <v>127984.416</v>
       </c>
       <c r="C8" s="29" t="n">
         <v>139511.891</v>
       </c>
       <c r="D8" s="30" t="n">
-        <v>0.3431</v>
+        <v>0.3429</v>
       </c>
       <c r="E8" s="30" t="n">
         <v>0.4683</v>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>133467.428</v>
+        <v>133509.808</v>
       </c>
       <c r="C9" s="29" t="n">
         <v>140817.396</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="B10" s="29" t="n">
-        <v>136276.52</v>
+        <v>136318.9</v>
       </c>
       <c r="C10" s="29" t="n">
         <v>147774.751</v>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="B11" s="29" t="n">
-        <v>147458.347</v>
+        <v>147500.727</v>
       </c>
       <c r="C11" s="29" t="n">
         <v>165710.24</v>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="B12" s="29" t="n">
-        <v>167797.844</v>
+        <v>167840.224</v>
       </c>
       <c r="C12" s="29" t="n">
         <v>178919.358</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>0.3115</v>
+        <v>0.3114</v>
       </c>
       <c r="E12" s="30" t="n">
         <v>0.2825</v>
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>175606.988</v>
+        <v>175649.368</v>
       </c>
       <c r="C13" s="29" t="n">
         <v>185354.246</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>180970.774</v>
+        <v>181013.154</v>
       </c>
       <c r="C14" s="29" t="n">
         <v>197336.297</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="B15" s="29" t="n">
-        <v>185703.815</v>
+        <v>185746.195</v>
       </c>
       <c r="C15" s="29" t="n">
         <v>197727.889</v>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="B16" s="29" t="n">
-        <v>199116.43</v>
+        <v>199158.81</v>
       </c>
       <c r="C16" s="29" t="n">
         <v>215863.072</v>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>211470.497</v>
+        <v>211512.877</v>
       </c>
       <c r="C17" s="29" t="n">
         <v>226563.945</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="B18" s="29" t="n">
-        <v>218784.626</v>
+        <v>218827.006</v>
       </c>
       <c r="C18" s="29" t="n">
         <v>237871.336</v>
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="B19" s="29" t="n">
-        <v>223283.589</v>
+        <v>223325.969</v>
       </c>
       <c r="C19" s="29" t="n">
         <v>224222.252</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.1214</v>
+        <v>0.1213</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0.0387</v>
@@ -3161,13 +3161,13 @@
         </is>
       </c>
       <c r="B20" s="29" t="n">
-        <v>228879.249</v>
+        <v>228921.629</v>
       </c>
       <c r="C20" s="29" t="n">
         <v>231898.758</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.1495</v>
+        <v>0.1494</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0.07429999999999999</v>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="B21" s="29" t="n">
-        <v>226004.365</v>
+        <v>226046.745</v>
       </c>
       <c r="C21" s="29" t="n">
         <v>233108.23905</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="B22" s="29" t="n">
-        <v>231347.002</v>
+        <v>231389.382</v>
       </c>
       <c r="C22" s="29" t="n">
         <v>233578.906</v>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="B23" s="29" t="n">
-        <v>241890.738</v>
+        <v>241933.118</v>
       </c>
       <c r="C23" s="29" t="n">
         <v>240012.8836</v>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="B24" s="29" t="n">
-        <v>262074.228</v>
+        <v>262116.608</v>
       </c>
       <c r="C24" s="29" t="n">
         <v>263176.32975</v>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="B25" s="29" t="n">
-        <v>262910.844</v>
+        <v>262953.224</v>
       </c>
       <c r="C25" s="29" t="n">
         <v>261187.7725</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="B26" s="29" t="n">
-        <v>273996.195</v>
+        <v>274038.575</v>
       </c>
       <c r="C26" s="29" t="n">
         <v>266305.1065</v>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>292146.173</v>
+        <v>292188.553</v>
       </c>
       <c r="C27" s="29" t="n">
         <v>280182.65</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="B28" s="29" t="n">
-        <v>318316.079</v>
+        <v>318358.459</v>
       </c>
       <c r="C28" s="29" t="n">
         <v>302402.543</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>329264.074</v>
+        <v>329306.454</v>
       </c>
       <c r="C29" s="29" t="n">
         <v>311756.2396</v>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="B30" s="29" t="n">
-        <v>351360.111</v>
+        <v>351402.491</v>
       </c>
       <c r="C30" s="29" t="n">
         <v>337488.7078</v>
@@ -3370,13 +3370,13 @@
         </is>
       </c>
       <c r="B31" s="29" t="n">
-        <v>367863.425</v>
+        <v>367905.805</v>
       </c>
       <c r="C31" s="29" t="n">
         <v>339271.879</v>
       </c>
       <c r="D31" s="30" t="n">
-        <v>0.1557</v>
+        <v>0.1556</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0.1219</v>
@@ -3395,7 +3395,7 @@
         <v>335619.0126</v>
       </c>
       <c r="D32" s="30" t="n">
-        <v>0.1847</v>
+        <v>0.1846</v>
       </c>
       <c r="E32" s="30" t="n">
         <v>0.1098</v>
@@ -5596,19 +5596,19 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>21702.85</v>
+        <v>42.38</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>18345.796</v>
+        <v>42.38</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>15123.396</v>
+        <v>42.38</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>20244.697</v>
+        <v>42.38</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>43794.655</v>
+        <v>0</v>
       </c>
       <c r="G4" s="10">
         <f>F4*(1+'02_Assumptions'!G4)</f>

--- a/Bao cao/VIB/VIB_Model_2026-06.xlsx
+++ b/Bao cao/VIB/VIB_Model_2026-06.xlsx
@@ -2803,12 +2803,12 @@
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>Tăng trưởng Tín dụng YTD (%)</t>
+          <t>Tăng trưởng Tín dụng QoQ (%)</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>Tăng trưởng Huy động YTD (%)</t>
+          <t>Tăng trưởng Huy động QoQ (%)</t>
         </is>
       </c>
     </row>
@@ -2825,10 +2825,10 @@
         <v>82885.63</v>
       </c>
       <c r="D2" s="30" t="n">
-        <v>0</v>
+        <v>0.0342</v>
       </c>
       <c r="E2" s="30" t="n">
-        <v>0</v>
+        <v>0.0074</v>
       </c>
     </row>
     <row r="3">
@@ -2863,10 +2863,10 @@
         <v>95015.06099999999</v>
       </c>
       <c r="D4" s="30" t="n">
-        <v>0.0866</v>
+        <v>0.0621</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>0.1463</v>
+        <v>0.0678</v>
       </c>
     </row>
     <row r="5">
@@ -2901,10 +2901,10 @@
         <v>114415.413</v>
       </c>
       <c r="D6" s="30" t="n">
-        <v>0.1902</v>
+        <v>0.124</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>0.2042</v>
+        <v>0.1543</v>
       </c>
     </row>
     <row r="7">
@@ -2920,10 +2920,10 @@
         <v>128964.391</v>
       </c>
       <c r="D7" s="30" t="n">
-        <v>0.2802</v>
+        <v>0.0756</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>0.3573</v>
+        <v>0.1272</v>
       </c>
     </row>
     <row r="8">
@@ -2939,10 +2939,10 @@
         <v>139511.891</v>
       </c>
       <c r="D8" s="30" t="n">
-        <v>0.3429</v>
+        <v>0.049</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>0.4683</v>
+        <v>0.0818</v>
       </c>
     </row>
     <row r="9">
@@ -2977,10 +2977,10 @@
         <v>147774.751</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>0.06509999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="E10" s="30" t="n">
-        <v>0.0592</v>
+        <v>0.04940000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2996,10 +2996,10 @@
         <v>165710.24</v>
       </c>
       <c r="D11" s="30" t="n">
-        <v>0.1525</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="E11" s="30" t="n">
-        <v>0.1878</v>
+        <v>0.1214</v>
       </c>
     </row>
     <row r="12">
@@ -3015,10 +3015,10 @@
         <v>178919.358</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>0.3114</v>
+        <v>0.1379</v>
       </c>
       <c r="E12" s="30" t="n">
-        <v>0.2825</v>
+        <v>0.07969999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -3053,10 +3053,10 @@
         <v>197336.297</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.0785</v>
+        <v>0.0305</v>
       </c>
       <c r="E14" s="30" t="n">
-        <v>0.1029</v>
+        <v>0.0646</v>
       </c>
     </row>
     <row r="15">
@@ -3072,10 +3072,10 @@
         <v>197727.889</v>
       </c>
       <c r="D15" s="30" t="n">
-        <v>0.1067</v>
+        <v>0.0261</v>
       </c>
       <c r="E15" s="30" t="n">
-        <v>0.1051</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="16">
@@ -3091,10 +3091,10 @@
         <v>215863.072</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>0.1866</v>
+        <v>0.0722</v>
       </c>
       <c r="E16" s="30" t="n">
-        <v>0.2065</v>
+        <v>0.0917</v>
       </c>
     </row>
     <row r="17">
@@ -3129,10 +3129,10 @@
         <v>237871.336</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>0.09880000000000001</v>
+        <v>0.0346</v>
       </c>
       <c r="E18" s="30" t="n">
-        <v>0.102</v>
+        <v>0.0499</v>
       </c>
     </row>
     <row r="19">
@@ -3148,10 +3148,10 @@
         <v>224222.252</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.1213</v>
+        <v>0.0206</v>
       </c>
       <c r="E19" s="30" t="n">
-        <v>0.0387</v>
+        <v>-0.0574</v>
       </c>
     </row>
     <row r="20">
@@ -3167,10 +3167,10 @@
         <v>231898.758</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.1494</v>
+        <v>0.0251</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>0.07429999999999999</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="21">
@@ -3205,10 +3205,10 @@
         <v>233578.906</v>
       </c>
       <c r="D22" s="30" t="n">
-        <v>0.0108</v>
+        <v>0.0236</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>0.0072</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="23">
@@ -3224,10 +3224,10 @@
         <v>240012.8836</v>
       </c>
       <c r="D23" s="30" t="n">
-        <v>0.0568</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="E23" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
     </row>
     <row r="24">
@@ -3243,10 +3243,10 @@
         <v>263176.32975</v>
       </c>
       <c r="D24" s="30" t="n">
-        <v>0.145</v>
+        <v>0.0834</v>
       </c>
       <c r="E24" s="30" t="n">
-        <v>0.1349</v>
+        <v>0.0965</v>
       </c>
     </row>
     <row r="25">
@@ -3281,10 +3281,10 @@
         <v>266305.1065</v>
       </c>
       <c r="D26" s="30" t="n">
-        <v>0.0455</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="E26" s="30" t="n">
-        <v>0.0119</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="27">
@@ -3300,10 +3300,10 @@
         <v>280182.65</v>
       </c>
       <c r="D27" s="30" t="n">
-        <v>0.1147</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="E27" s="30" t="n">
-        <v>0.0646</v>
+        <v>0.0521</v>
       </c>
     </row>
     <row r="28">
@@ -3319,10 +3319,10 @@
         <v>302402.543</v>
       </c>
       <c r="D28" s="30" t="n">
-        <v>0.2146</v>
+        <v>0.08960000000000001</v>
       </c>
       <c r="E28" s="30" t="n">
-        <v>0.149</v>
+        <v>0.0793</v>
       </c>
     </row>
     <row r="29">
@@ -3357,10 +3357,10 @@
         <v>337488.7078</v>
       </c>
       <c r="D30" s="30" t="n">
-        <v>0.1038</v>
+        <v>0.06709999999999999</v>
       </c>
       <c r="E30" s="30" t="n">
-        <v>0.116</v>
+        <v>0.0825</v>
       </c>
     </row>
     <row r="31">
@@ -3376,10 +3376,10 @@
         <v>339271.879</v>
       </c>
       <c r="D31" s="30" t="n">
-        <v>0.1556</v>
+        <v>0.047</v>
       </c>
       <c r="E31" s="30" t="n">
-        <v>0.1219</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="32">
@@ -3395,10 +3395,10 @@
         <v>335619.0126</v>
       </c>
       <c r="D32" s="30" t="n">
-        <v>0.1846</v>
+        <v>0.025</v>
       </c>
       <c r="E32" s="30" t="n">
-        <v>0.1098</v>
+        <v>-0.0108</v>
       </c>
     </row>
     <row r="33">

--- a/Bao cao/VIB/VIB_Model_2026-06.xlsx
+++ b/Bao cao/VIB/VIB_Model_2026-06.xlsx
@@ -25,6 +25,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Summary_Snapshot" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_PE_PB_History" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Credit_Funding_Growth" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_Peer_Benchmark" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +40,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,8 +98,14 @@
       <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -123,6 +130,18 @@
         <bgColor rgb="00FFFF99"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -142,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,6 +203,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="1" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="1" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3425,6 +3452,669 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Ngân hàng</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>NPL (%)</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>NIM (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>CASA (%)</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>ROE (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>CIR (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>P/B (x)</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Tăng trưởng tín dụng (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Vốn hóa (tỷ VND)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>Trung bình ngành</t>
+        </is>
+      </c>
+      <c r="B2" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D2" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" s="32" t="n">
+        <v>35</v>
+      </c>
+      <c r="G2" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>VCB — Vietcombank</t>
+        </is>
+      </c>
+      <c r="B3" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C3" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D3" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E3" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F3" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G3" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I3" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>BID — BIDV</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C4" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D4" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F4" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G4" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I4" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>CTG — VietinBank</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>TCB — Techcombank</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G6" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I6" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>MBB — MBBank</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G7" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I7" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>ACB — ACB</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G8" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>VIB — VIB</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E9" s="36" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F9" s="36" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G9" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="36" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I9" s="38" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>HDB — HDBank</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G10" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>STB — Sacombank</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G11" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>VPB — VPBank</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G12" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>TPB — TPBank</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G13" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>MSB — MSB</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G14" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>EIB — Eximbank</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G15" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>LPB — LienVietPostBank</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G16" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>SHB — SHB</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G17" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>OCB — OCB</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G18" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I18" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>BAB — BacABank</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G19" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I19" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>NAB — NamABank</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G20" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Bao cao/VIB/VIB_Model_2026-06.xlsx
+++ b/Bao cao/VIB/VIB_Model_2026-06.xlsx
@@ -3526,25 +3526,25 @@
         </is>
       </c>
       <c r="B2" s="32" t="n">
-        <v>2</v>
+        <v>2.385</v>
       </c>
       <c r="C2" s="32" t="n">
-        <v>3.5</v>
+        <v>4.357222222222222</v>
       </c>
       <c r="D2" s="32" t="n">
-        <v>20</v>
+        <v>16.84888888888889</v>
       </c>
       <c r="E2" s="32" t="n">
-        <v>15</v>
+        <v>15.58666666666667</v>
       </c>
       <c r="F2" s="32" t="n">
-        <v>35</v>
+        <v>33.94777777777777</v>
       </c>
       <c r="G2" s="33" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="32" t="n">
-        <v>12</v>
+        <v>3.509444444444445</v>
       </c>
       <c r="I2" s="31" t="inlineStr">
         <is>
@@ -3559,28 +3559,28 @@
         </is>
       </c>
       <c r="B3" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0063</v>
       </c>
       <c r="C3" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0409</v>
       </c>
       <c r="D3" s="30" t="n">
-        <v>0.2</v>
+        <v>0.3255</v>
       </c>
       <c r="E3" s="30" t="n">
-        <v>0.15</v>
+        <v>0.1617</v>
       </c>
       <c r="F3" s="30" t="n">
-        <v>0.35</v>
+        <v>0.325</v>
       </c>
       <c r="G3" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0478</v>
       </c>
       <c r="I3" s="29" t="n">
-        <v>50000</v>
+        <v>513038.4507716</v>
       </c>
     </row>
     <row r="4">
@@ -3590,28 +3590,28 @@
         </is>
       </c>
       <c r="B4" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0178</v>
       </c>
       <c r="C4" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0263</v>
       </c>
       <c r="D4" s="30" t="n">
-        <v>0.2</v>
+        <v>0.1949</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>0.15</v>
+        <v>0.1443</v>
       </c>
       <c r="F4" s="30" t="n">
-        <v>0.35</v>
+        <v>0.3202</v>
       </c>
       <c r="G4" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0233</v>
       </c>
       <c r="I4" s="29" t="n">
-        <v>50000</v>
+        <v>303578.719257</v>
       </c>
     </row>
     <row r="5">
@@ -3621,28 +3621,28 @@
         </is>
       </c>
       <c r="B5" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0103</v>
       </c>
       <c r="C5" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0389</v>
       </c>
       <c r="D5" s="30" t="n">
-        <v>0.2</v>
+        <v>0.2408</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>0.15</v>
+        <v>0.1899</v>
       </c>
       <c r="F5" s="30" t="n">
-        <v>0.35</v>
+        <v>0.2494</v>
       </c>
       <c r="G5" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0187</v>
       </c>
       <c r="I5" s="29" t="n">
-        <v>50000</v>
+        <v>260969.3398032</v>
       </c>
     </row>
     <row r="6">
@@ -3652,28 +3652,28 @@
         </is>
       </c>
       <c r="B6" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0111</v>
       </c>
       <c r="C6" s="30" t="n">
-        <v>0.035</v>
+        <v>0.04849999999999999</v>
       </c>
       <c r="D6" s="30" t="n">
-        <v>0.2</v>
+        <v>0.3145</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>0.15</v>
+        <v>0.1489</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>0.35</v>
+        <v>0.2829</v>
       </c>
       <c r="G6" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>0.12</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>50000</v>
+        <v>236680.4298276</v>
       </c>
     </row>
     <row r="7">
@@ -3683,28 +3683,28 @@
         </is>
       </c>
       <c r="B7" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0144</v>
       </c>
       <c r="C7" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0539</v>
       </c>
       <c r="D7" s="30" t="n">
-        <v>0.2</v>
+        <v>0.3227</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>0.15</v>
+        <v>0.2058</v>
       </c>
       <c r="F7" s="30" t="n">
-        <v>0.35</v>
+        <v>0.2494</v>
       </c>
       <c r="G7" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0327</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>50000</v>
+        <v>199361.24774775</v>
       </c>
     </row>
     <row r="8">
@@ -3714,28 +3714,28 @@
         </is>
       </c>
       <c r="B8" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0098</v>
       </c>
       <c r="C8" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0399</v>
       </c>
       <c r="D8" s="30" t="n">
-        <v>0.2</v>
+        <v>0.2123</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>0.15</v>
+        <v>0.175</v>
       </c>
       <c r="F8" s="30" t="n">
-        <v>0.35</v>
+        <v>0.3201</v>
       </c>
       <c r="G8" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0325</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>50000</v>
+        <v>131179.9362282</v>
       </c>
     </row>
     <row r="9">
@@ -3745,28 +3745,28 @@
         </is>
       </c>
       <c r="B9" s="36" t="n">
-        <v>0.02</v>
+        <v>0.0298</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0.035</v>
+        <v>0.0424</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>0.2</v>
+        <v>0.1393</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>0.15</v>
+        <v>0.1824</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>0.35</v>
+        <v>0.3161</v>
       </c>
       <c r="G9" s="37" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>0.12</v>
+        <v>0.0113</v>
       </c>
       <c r="I9" s="38" t="n">
-        <v>50000</v>
+        <v>54974.6922165</v>
       </c>
     </row>
     <row r="10">
@@ -3776,28 +3776,28 @@
         </is>
       </c>
       <c r="B10" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0264</v>
       </c>
       <c r="C10" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0572</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>0.2</v>
+        <v>0.1021</v>
       </c>
       <c r="E10" s="30" t="n">
-        <v>0.15</v>
+        <v>0.2357</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>0.35</v>
+        <v>0.2599</v>
       </c>
       <c r="G10" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>0.12</v>
+        <v>0.1006</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>50000</v>
+        <v>127134.0186042</v>
       </c>
     </row>
     <row r="11">
@@ -3807,28 +3807,28 @@
         </is>
       </c>
       <c r="B11" s="30" t="n">
-        <v>0.02</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="C11" s="30" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="D11" s="30" t="n">
-        <v>0.2</v>
+        <v>0.1592</v>
       </c>
       <c r="E11" s="30" t="n">
-        <v>0.15</v>
+        <v>0.1031</v>
       </c>
       <c r="F11" s="30" t="n">
-        <v>0.35</v>
+        <v>0.4521</v>
       </c>
       <c r="G11" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="30" t="n">
-        <v>0.12</v>
+        <v>-0.0024</v>
       </c>
       <c r="I11" s="29" t="n">
-        <v>50000</v>
+        <v>138940.3982692</v>
       </c>
     </row>
     <row r="12">
@@ -3838,28 +3838,28 @@
         </is>
       </c>
       <c r="B12" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0365</v>
       </c>
       <c r="C12" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0664</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>0.2</v>
+        <v>0.1309</v>
       </c>
       <c r="E12" s="30" t="n">
-        <v>0.15</v>
+        <v>0.1357</v>
       </c>
       <c r="F12" s="30" t="n">
-        <v>0.35</v>
+        <v>0.2169</v>
       </c>
       <c r="G12" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="30" t="n">
-        <v>0.12</v>
+        <v>0.1023</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>50000</v>
+        <v>212232.45632675</v>
       </c>
     </row>
     <row r="13">
@@ -3869,28 +3869,28 @@
         </is>
       </c>
       <c r="B13" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0219</v>
       </c>
       <c r="C13" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0443</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2</v>
+        <v>0.1745</v>
       </c>
       <c r="E13" s="30" t="n">
-        <v>0.15</v>
+        <v>0.1401</v>
       </c>
       <c r="F13" s="30" t="n">
-        <v>0.35</v>
+        <v>0.4585</v>
       </c>
       <c r="G13" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0326</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>50000</v>
+        <v>44662.1546553</v>
       </c>
     </row>
     <row r="14">
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B14" s="30" t="n">
-        <v>0.02</v>
+        <v>0.027</v>
       </c>
       <c r="C14" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0604</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2</v>
+        <v>0.2551</v>
       </c>
       <c r="E14" s="30" t="n">
-        <v>0.15</v>
+        <v>0.1377</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>0.35</v>
+        <v>0.3451</v>
       </c>
       <c r="G14" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0464</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>50000</v>
+        <v>49608</v>
       </c>
     </row>
     <row r="15">
@@ -3931,28 +3931,28 @@
         </is>
       </c>
       <c r="B15" s="30" t="n">
-        <v>0.02</v>
+        <v>0.031</v>
       </c>
       <c r="C15" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0295</v>
       </c>
       <c r="D15" s="30" t="n">
-        <v>0.2</v>
+        <v>0.1337</v>
       </c>
       <c r="E15" s="30" t="n">
-        <v>0.15</v>
+        <v>0.0407</v>
       </c>
       <c r="F15" s="30" t="n">
-        <v>0.35</v>
+        <v>0.5698</v>
       </c>
       <c r="G15" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0289</v>
       </c>
       <c r="I15" s="29" t="n">
-        <v>50000</v>
+        <v>38372.0445042</v>
       </c>
     </row>
     <row r="16">
@@ -3962,28 +3962,28 @@
         </is>
       </c>
       <c r="B16" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0186</v>
       </c>
       <c r="C16" s="30" t="n">
-        <v>0.035</v>
+        <v>0.039</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>0.2</v>
+        <v>0.0649</v>
       </c>
       <c r="E16" s="30" t="n">
-        <v>0.15</v>
+        <v>0.1843</v>
       </c>
       <c r="F16" s="30" t="n">
-        <v>0.35</v>
+        <v>0.3014</v>
       </c>
       <c r="G16" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0284</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>50000</v>
+        <v>158325.9513</v>
       </c>
     </row>
     <row r="17">
@@ -3993,28 +3993,28 @@
         </is>
       </c>
       <c r="B17" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0265</v>
       </c>
       <c r="C17" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0357</v>
       </c>
       <c r="D17" s="30" t="n">
-        <v>0.2</v>
+        <v>0.0663</v>
       </c>
       <c r="E17" s="30" t="n">
-        <v>0.15</v>
+        <v>0.2078</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>0.35</v>
+        <v>0.1717</v>
       </c>
       <c r="G17" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0201</v>
       </c>
       <c r="I17" s="29" t="n">
-        <v>50000</v>
+        <v>72941.55738870001</v>
       </c>
     </row>
     <row r="18">
@@ -4024,28 +4024,28 @@
         </is>
       </c>
       <c r="B18" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0359</v>
       </c>
       <c r="C18" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0475</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>0.2</v>
+        <v>0.1067</v>
       </c>
       <c r="E18" s="30" t="n">
-        <v>0.15</v>
+        <v>0.1118</v>
       </c>
       <c r="F18" s="30" t="n">
-        <v>0.35</v>
+        <v>0.3709</v>
       </c>
       <c r="G18" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0272</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>50000</v>
+        <v>33820.7640068</v>
       </c>
     </row>
     <row r="19">
@@ -4055,28 +4055,28 @@
         </is>
       </c>
       <c r="B19" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0191</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0319</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.2</v>
+        <v>0.0305</v>
       </c>
       <c r="E19" s="30" t="n">
-        <v>0.15</v>
+        <v>0.0882</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>0.35</v>
+        <v>0.5122</v>
       </c>
       <c r="G19" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0246</v>
       </c>
       <c r="I19" s="29" t="n">
-        <v>50000</v>
+        <v>13715.3535204</v>
       </c>
     </row>
     <row r="20">
@@ -4086,28 +4086,28 @@
         </is>
       </c>
       <c r="B20" s="30" t="n">
-        <v>0.02</v>
+        <v>0.0183</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.035</v>
+        <v>0.0416</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.2</v>
+        <v>0.05889999999999999</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>0.15</v>
+        <v>0.2125</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>0.35</v>
+        <v>0.389</v>
       </c>
       <c r="G20" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="30" t="n">
-        <v>0.12</v>
+        <v>0.0191</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>50000</v>
+        <v>28172.6307801</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIB/VIB_Model_2026-06.xlsx
+++ b/Bao cao/VIB/VIB_Model_2026-06.xlsx
@@ -3541,7 +3541,7 @@
         <v>33.94777777777777</v>
       </c>
       <c r="G2" s="33" t="n">
-        <v>1</v>
+        <v>1.443888888888889</v>
       </c>
       <c r="H2" s="32" t="n">
         <v>3.509444444444445</v>
@@ -3574,7 +3574,7 @@
         <v>0.325</v>
       </c>
       <c r="G3" s="34" t="n">
-        <v>1</v>
+        <v>2.19</v>
       </c>
       <c r="H3" s="30" t="n">
         <v>0.0478</v>
@@ -3605,7 +3605,7 @@
         <v>0.3202</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>1</v>
+        <v>1.59</v>
       </c>
       <c r="H4" s="30" t="n">
         <v>0.0233</v>
@@ -3636,7 +3636,7 @@
         <v>0.2494</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="H5" s="30" t="n">
         <v>0.0187</v>
@@ -3667,7 +3667,7 @@
         <v>0.2829</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="H6" s="30" t="n">
         <v>0.03759999999999999</v>
@@ -3698,7 +3698,7 @@
         <v>0.2494</v>
       </c>
       <c r="G7" s="34" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="H7" s="30" t="n">
         <v>0.0327</v>
@@ -3729,7 +3729,7 @@
         <v>0.3201</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="H8" s="30" t="n">
         <v>0.0325</v>
@@ -3760,7 +3760,7 @@
         <v>0.3161</v>
       </c>
       <c r="G9" s="37" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="H9" s="36" t="n">
         <v>0.0113</v>
@@ -3791,7 +3791,7 @@
         <v>0.2599</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>1</v>
+        <v>1.53</v>
       </c>
       <c r="H10" s="30" t="n">
         <v>0.1006</v>
@@ -3822,7 +3822,7 @@
         <v>0.4521</v>
       </c>
       <c r="G11" s="34" t="n">
-        <v>1</v>
+        <v>2.26</v>
       </c>
       <c r="H11" s="30" t="n">
         <v>-0.0024</v>
@@ -3853,7 +3853,7 @@
         <v>0.2169</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="H12" s="30" t="n">
         <v>0.1023</v>
@@ -3884,7 +3884,7 @@
         <v>0.4585</v>
       </c>
       <c r="G13" s="34" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="H13" s="30" t="n">
         <v>0.0326</v>
@@ -3915,7 +3915,7 @@
         <v>0.3451</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="H14" s="30" t="n">
         <v>0.0464</v>
@@ -3946,7 +3946,7 @@
         <v>0.5698</v>
       </c>
       <c r="G15" s="34" t="n">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="H15" s="30" t="n">
         <v>0.0289</v>
@@ -3977,7 +3977,7 @@
         <v>0.3014</v>
       </c>
       <c r="G16" s="34" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="H16" s="30" t="n">
         <v>0.0284</v>
@@ -4008,7 +4008,7 @@
         <v>0.1717</v>
       </c>
       <c r="G17" s="34" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="H17" s="30" t="n">
         <v>0.0201</v>
@@ -4039,7 +4039,7 @@
         <v>0.3709</v>
       </c>
       <c r="G18" s="34" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H18" s="30" t="n">
         <v>0.0272</v>
@@ -4070,7 +4070,7 @@
         <v>0.5122</v>
       </c>
       <c r="G19" s="34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H19" s="30" t="n">
         <v>0.0246</v>
@@ -4101,7 +4101,7 @@
         <v>0.389</v>
       </c>
       <c r="G20" s="34" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="H20" s="30" t="n">
         <v>0.0191</v>
